--- a/C. Financeiro 3.2.xlsx
+++ b/C. Financeiro 3.2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rcssi\Code\Python\Python\Projects\Automate_Python\Report_Budget\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rcssi\Code\Personal_Finance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B82E17AD-D101-4E6B-9359-112ACC062BC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93A38CFF-437C-4C33-AF63-68576D29E7E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-114" yWindow="-114" windowWidth="19704" windowHeight="11178" tabRatio="792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="63">
   <si>
     <t>Mês</t>
   </si>
@@ -259,6 +259,9 @@
   </si>
   <si>
     <t>Perdas Outros</t>
+  </si>
+  <si>
+    <t>Transferir</t>
   </si>
 </sst>
 </file>
@@ -589,7 +592,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -827,24 +830,6 @@
     </xf>
     <xf numFmtId="44" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -856,6 +841,39 @@
     </xf>
     <xf numFmtId="44" fontId="10" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2711,7 +2729,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>150</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0</c:v>
@@ -3064,7 +3082,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0</c:v>
@@ -3459,7 +3477,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>150</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -3468,7 +3486,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6564,8 +6582,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{739BA625-5E32-4F47-8323-C47308DEF24A}" name="Tabela1" displayName="Tabela1" ref="B9:H12" insertRowShift="1" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
-  <autoFilter ref="B9:H12" xr:uid="{739BA625-5E32-4F47-8323-C47308DEF24A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{739BA625-5E32-4F47-8323-C47308DEF24A}" name="Tabela1" displayName="Tabela1" ref="B9:H13" insertRowShift="1" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
+  <autoFilter ref="B9:H13" xr:uid="{739BA625-5E32-4F47-8323-C47308DEF24A}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B10:H22">
     <sortCondition ref="B9:B22"/>
   </sortState>
@@ -6874,7 +6892,7 @@
   <sheetPr codeName="Planilha1">
     <tabColor theme="0"/>
   </sheetPr>
-  <dimension ref="A2:I548"/>
+  <dimension ref="A2:I549"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" style="82" customWidth="1"/>
@@ -6890,15 +6908,15 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="101" t="s">
+      <c r="B2" s="105" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="101"/>
-      <c r="D2" s="101" t="str">
+      <c r="C2" s="105"/>
+      <c r="D2" s="105" t="str">
         <f ca="1">PROPER(TEXT(TODAY(),"MMMM"))</f>
         <v>Outubro</v>
       </c>
-      <c r="E2" s="101"/>
+      <c r="E2" s="105"/>
       <c r="F2" s="83"/>
       <c r="H2" s="82"/>
     </row>
@@ -6908,14 +6926,14 @@
       </c>
       <c r="C3" s="7" cm="1">
         <f t="array" aca="1" ref="C3" ca="1">SUM(SUMIFS(Tabela1[Valor],Tabela1[Operação],{"Receitas";"Transferir"},Tabela1[Alocação],B3,Tabela1[Data],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Valor],Tabela1[Operação],"&lt;&gt;Receitas",Tabela1[Operação],"&lt;&gt;Transferir",Tabela1[Alocação],B3,Tabela1[Data],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Valor],Tabela1[Categoria],B3,Tabela1[Data],"&lt;="&amp;(TODAY()))</f>
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D3" s="71" t="s">
         <v>58</v>
       </c>
       <c r="E3" s="56">
         <f ca="1">VLOOKUP(D2,'Gráfico - Anual'!A3:I14,8,FALSE)</f>
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="H3" s="82"/>
     </row>
@@ -6932,7 +6950,7 @@
       </c>
       <c r="E4" s="56">
         <f>'Gráfico - Anual'!I15</f>
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="F4" s="83"/>
       <c r="H4" s="82"/>
@@ -6950,7 +6968,7 @@
       </c>
       <c r="E5" s="56">
         <f ca="1">VLOOKUP(D2,'Gráfico - Anual'!A3:I14,9,FALSE)</f>
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="F5" s="83"/>
       <c r="H5" s="82"/>
@@ -6961,7 +6979,7 @@
       </c>
       <c r="C6" s="7">
         <f ca="1">SUM(C3:C5)</f>
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D6" s="66" t="s">
         <v>44</v>
@@ -6982,11 +7000,11 @@
       <c r="A8" s="68"/>
       <c r="B8" s="69">
         <f>SUBTOTAL(2,Tabela1[Data])</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G8" s="83">
         <f>SUBTOTAL(9,Tabela1[Valor])</f>
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H8" s="82"/>
     </row>
@@ -7018,7 +7036,7 @@
         <v>45200</v>
       </c>
       <c r="C10" s="78" t="str">
-        <f t="shared" ref="C10:C30" si="0">IF(ISBLANK(B10),"",PROPER(TEXT(B10,"MMMM")))</f>
+        <f t="shared" ref="C10:C31" si="0">IF(ISBLANK(B10),"",PROPER(TEXT(B10,"MMMM")))</f>
         <v>Outubro</v>
       </c>
       <c r="D10" s="78" t="s">
@@ -7036,60 +7054,86 @@
       <c r="H10" s="81"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B11" s="77"/>
+      <c r="B11" s="77">
+        <v>45200</v>
+      </c>
       <c r="C11" s="78" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="D11" s="78"/>
-      <c r="E11" s="79"/>
-      <c r="F11" s="79"/>
-      <c r="G11" s="80"/>
+        <v>Outubro</v>
+      </c>
+      <c r="D11" s="78" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11" s="79" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11" s="79" t="s">
+        <v>38</v>
+      </c>
+      <c r="G11" s="80">
+        <v>50</v>
+      </c>
       <c r="H11" s="81"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B12" s="77"/>
+      <c r="B12" s="77">
+        <v>45201</v>
+      </c>
       <c r="C12" s="78" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="D12" s="78"/>
-      <c r="E12" s="79"/>
-      <c r="F12" s="79"/>
-      <c r="G12" s="80"/>
+        <v>Outubro</v>
+      </c>
+      <c r="D12" s="78" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="79" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" s="79" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" s="111">
+        <v>50</v>
+      </c>
       <c r="H12" s="81"/>
     </row>
-    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C21" s="84" t="str">
-        <f>IF(ISBLANK(B21),"",PROPER(TEXT(B21,"MMMM")))</f>
-        <v/>
-      </c>
-      <c r="D21" s="84" t="str">
-        <f t="shared" ref="D21:G21" si="1">IF(ISBLANK(C21),"",PROPER(TEXT(C21,"MMMM")))</f>
-        <v/>
-      </c>
-      <c r="E21" s="84" t="str">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B13" s="112"/>
+      <c r="C13" s="113" t="str">
+        <f>IF(ISBLANK(B13),"",PROPER(TEXT(B13,"MMMM")))</f>
+        <v/>
+      </c>
+      <c r="D13" s="78"/>
+      <c r="E13" s="114"/>
+      <c r="F13" s="79"/>
+      <c r="G13" s="111"/>
+      <c r="H13" s="115"/>
+    </row>
+    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C22" s="84" t="str">
+        <f>IF(ISBLANK(B22),"",PROPER(TEXT(B22,"MMMM")))</f>
+        <v/>
+      </c>
+      <c r="D22" s="84" t="str">
+        <f t="shared" ref="D22:G22" si="1">IF(ISBLANK(C22),"",PROPER(TEXT(C22,"MMMM")))</f>
+        <v/>
+      </c>
+      <c r="E22" s="84" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F21" s="84" t="str">
+      <c r="F22" s="84" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G21" s="84" t="str">
+      <c r="G22" s="84" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="30" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C30" s="84" t="str">
-        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="31" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C31" s="84" t="str">
-        <f t="shared" ref="C31:C45" si="2">IF(ISBLANK(B31),"",PROPER(TEXT(B31,"MMMM")))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I31" s="82" t="s">
@@ -7098,13 +7142,13 @@
     </row>
     <row r="32" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C32" s="84" t="str">
-        <f t="shared" ref="C32:C42" si="3">IF(ISBLANK(B32),"",PROPER(TEXT(B32,"MMMM")))</f>
+        <f t="shared" ref="C32:C46" si="2">IF(ISBLANK(B32),"",PROPER(TEXT(B32,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C33" s="84" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="C33:C43" si="3">IF(ISBLANK(B33),"",PROPER(TEXT(B33,"MMMM")))</f>
         <v/>
       </c>
     </row>
@@ -7164,7 +7208,7 @@
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C43" s="84" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -7179,15 +7223,12 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G45" s="87"/>
-      <c r="H45" s="88"/>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B46" s="82"/>
-      <c r="C46" s="82"/>
-      <c r="D46" s="82"/>
-      <c r="E46" s="68"/>
-      <c r="F46" s="68"/>
+      <c r="C46" s="84" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="G46" s="87"/>
       <c r="H46" s="88"/>
     </row>
@@ -7211,8 +7252,8 @@
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B49" s="82"/>
-      <c r="C49" s="89"/>
-      <c r="D49" s="89"/>
+      <c r="C49" s="82"/>
+      <c r="D49" s="82"/>
       <c r="E49" s="68"/>
       <c r="F49" s="68"/>
       <c r="G49" s="87"/>
@@ -7220,9 +7261,12 @@
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B50" s="82"/>
-      <c r="C50" s="82"/>
-      <c r="D50" s="82"/>
-      <c r="G50" s="82"/>
+      <c r="C50" s="89"/>
+      <c r="D50" s="89"/>
+      <c r="E50" s="68"/>
+      <c r="F50" s="68"/>
+      <c r="G50" s="87"/>
+      <c r="H50" s="88"/>
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B51" s="82"/>
@@ -7261,14 +7305,14 @@
       <c r="G56" s="82"/>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C57" s="84" t="str">
-        <f t="shared" ref="C57:C115" si="4">IF(ISBLANK(B57),"",PROPER(TEXT(B57,"MMMM")))</f>
-        <v/>
-      </c>
+      <c r="B57" s="82"/>
+      <c r="C57" s="82"/>
+      <c r="D57" s="82"/>
+      <c r="G57" s="82"/>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C58" s="84" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="C58:C116" si="4">IF(ISBLANK(B58),"",PROPER(TEXT(B58,"MMMM")))</f>
         <v/>
       </c>
     </row>
@@ -7616,13 +7660,13 @@
     </row>
     <row r="116" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C116" s="84" t="str">
-        <f t="shared" ref="C116:C179" si="5">IF(ISBLANK(B116),"",PROPER(TEXT(B116,"MMMM")))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="117" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C117" s="84" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="C117:C180" si="5">IF(ISBLANK(B117),"",PROPER(TEXT(B117,"MMMM")))</f>
         <v/>
       </c>
     </row>
@@ -8000,13 +8044,13 @@
     </row>
     <row r="180" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C180" s="84" t="str">
-        <f t="shared" ref="C180:C243" si="6">IF(ISBLANK(B180),"",PROPER(TEXT(B180,"MMMM")))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="181" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C181" s="84" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="C181:C244" si="6">IF(ISBLANK(B181),"",PROPER(TEXT(B181,"MMMM")))</f>
         <v/>
       </c>
     </row>
@@ -8384,13 +8428,13 @@
     </row>
     <row r="244" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C244" s="84" t="str">
-        <f t="shared" ref="C244:C307" si="7">IF(ISBLANK(B244),"",PROPER(TEXT(B244,"MMMM")))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="245" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C245" s="84" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="C245:C308" si="7">IF(ISBLANK(B245),"",PROPER(TEXT(B245,"MMMM")))</f>
         <v/>
       </c>
     </row>
@@ -8768,13 +8812,13 @@
     </row>
     <row r="308" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C308" s="84" t="str">
-        <f t="shared" ref="C308:C371" si="8">IF(ISBLANK(B308),"",PROPER(TEXT(B308,"MMMM")))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="309" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C309" s="84" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="C309:C372" si="8">IF(ISBLANK(B309),"",PROPER(TEXT(B309,"MMMM")))</f>
         <v/>
       </c>
     </row>
@@ -9152,13 +9196,13 @@
     </row>
     <row r="372" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C372" s="84" t="str">
-        <f t="shared" ref="C372:C435" si="9">IF(ISBLANK(B372),"",PROPER(TEXT(B372,"MMMM")))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="373" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C373" s="84" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="C373:C436" si="9">IF(ISBLANK(B373),"",PROPER(TEXT(B373,"MMMM")))</f>
         <v/>
       </c>
     </row>
@@ -9536,13 +9580,13 @@
     </row>
     <row r="436" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C436" s="84" t="str">
-        <f t="shared" ref="C436:C499" si="10">IF(ISBLANK(B436),"",PROPER(TEXT(B436,"MMMM")))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="437" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C437" s="84" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="C437:C500" si="10">IF(ISBLANK(B437),"",PROPER(TEXT(B437,"MMMM")))</f>
         <v/>
       </c>
     </row>
@@ -9920,13 +9964,13 @@
     </row>
     <row r="500" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C500" s="84" t="str">
-        <f t="shared" ref="C500:C548" si="11">IF(ISBLANK(B500),"",PROPER(TEXT(B500,"MMMM")))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="501" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C501" s="84" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="C501:C549" si="11">IF(ISBLANK(B501),"",PROPER(TEXT(B501,"MMMM")))</f>
         <v/>
       </c>
     </row>
@@ -10208,6 +10252,12 @@
     </row>
     <row r="548" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C548" s="84" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="549" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C549" s="84" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
@@ -10226,14 +10276,14 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E10:E20" xr:uid="{E4F2BDDC-1223-4DFF-8087-7B85DF038B73}">
+  <dataValidations disablePrompts="1" count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E10:E21" xr:uid="{E4F2BDDC-1223-4DFF-8087-7B85DF038B73}">
       <formula1>INDIRECT(D10)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D10:D20" xr:uid="{4E564D7B-00FF-4101-8D9D-5EA4D9B1919A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D10:D21" xr:uid="{4E564D7B-00FF-4101-8D9D-5EA4D9B1919A}">
       <formula1>"Receitas, Perdas, Investimentos, Despesas, Transferir"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F10:F20" xr:uid="{0D51CC9B-6F94-4F85-BAFC-26C786BB30BC}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F10:F21" xr:uid="{0D51CC9B-6F94-4F85-BAFC-26C786BB30BC}">
       <formula1>Ativos</formula1>
     </dataValidation>
   </dataValidations>
@@ -10727,7 +10777,7 @@
         <v>0</v>
       </c>
       <c r="C13" s="76">
-        <f t="shared" ref="C13:M13" si="0">IF((SUM(C4:C6)-SUM(C9:C11)) &gt; 10, ((SUM(C4:C6)-SUM(C9:C11))*0.1), (0))-C12</f>
+        <f t="shared" ref="C13:L13" si="0">IF((SUM(C4:C6)-SUM(C9:C11)) &gt; 10, ((SUM(C4:C6)-SUM(C9:C11))*0.1), (0))-C12</f>
         <v>0</v>
       </c>
       <c r="D13" s="76">
@@ -10845,7 +10895,7 @@
       </c>
       <c r="K16" s="7">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],K$2,Tabela1[Categoria],$A16)</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L16" s="7">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],L$2,Tabela1[Categoria],$A16)</f>
@@ -10933,7 +10983,7 @@
         <v>0</v>
       </c>
       <c r="C19" s="7">
-        <f t="shared" ref="B19:M19" si="1">ROUND(SUM(C4:C6)-SUM(C16:C17)-SUM(C9:C12),2)</f>
+        <f t="shared" ref="C19:L19" si="1">ROUND(SUM(C4:C6)-SUM(C16:C17)-SUM(C9:C12),2)</f>
         <v>0</v>
       </c>
       <c r="D19" s="7">
@@ -10966,7 +11016,7 @@
       </c>
       <c r="K19" s="7">
         <f t="shared" si="1"/>
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="L19" s="7">
         <f t="shared" si="1"/>
@@ -11154,7 +11204,7 @@
       <c r="AD3" s="38"/>
       <c r="AE3" s="4">
         <f>'Receitas - Mapa'!K19</f>
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="AG3" s="38"/>
       <c r="AH3" s="4">
@@ -11220,17 +11270,17 @@
       <c r="AC4" s="40"/>
       <c r="AE4" s="51">
         <f>AE3-(SUM(AE7:AE15))+AB4</f>
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="AF4" s="40"/>
       <c r="AH4" s="51">
         <f>AH3-(SUM(AH7:AH15))+AE4</f>
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="AI4" s="40"/>
       <c r="AK4" s="51">
         <f>AK3-SUM(AK7:AK15)+AH4</f>
-        <v>150</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -11273,7 +11323,7 @@
       <c r="AK5" s="39"/>
     </row>
     <row r="6" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="104" t="s">
+      <c r="A6" s="106" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="42"/>
@@ -11362,7 +11412,7 @@
       </c>
     </row>
     <row r="7" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="104"/>
+      <c r="A7" s="106"/>
       <c r="B7" s="42"/>
       <c r="C7" s="2" t="s">
         <v>27</v>
@@ -11472,7 +11522,7 @@
       </c>
     </row>
     <row r="8" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="104"/>
+      <c r="A8" s="106"/>
       <c r="B8" s="42"/>
       <c r="C8" s="2" t="s">
         <v>25</v>
@@ -11571,7 +11621,7 @@
       </c>
     </row>
     <row r="9" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="104"/>
+      <c r="A9" s="106"/>
       <c r="B9" s="42"/>
       <c r="C9" s="3" t="s">
         <v>26</v>
@@ -11670,7 +11720,7 @@
       </c>
     </row>
     <row r="10" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="104"/>
+      <c r="A10" s="106"/>
       <c r="B10" s="42"/>
       <c r="C10" s="3" t="s">
         <v>24</v>
@@ -11769,7 +11819,7 @@
       </c>
     </row>
     <row r="11" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="104"/>
+      <c r="A11" s="106"/>
       <c r="B11" s="42"/>
       <c r="C11" s="3" t="s">
         <v>23</v>
@@ -11868,7 +11918,7 @@
       </c>
     </row>
     <row r="12" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="104"/>
+      <c r="A12" s="106"/>
       <c r="B12" s="42"/>
       <c r="C12" s="3" t="s">
         <v>28</v>
@@ -11967,7 +12017,7 @@
       </c>
     </row>
     <row r="13" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="104"/>
+      <c r="A13" s="106"/>
       <c r="B13" s="42"/>
       <c r="C13" s="3" t="s">
         <v>13</v>
@@ -12066,7 +12116,7 @@
       </c>
     </row>
     <row r="14" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="104"/>
+      <c r="A14" s="106"/>
       <c r="B14" s="42"/>
       <c r="C14" s="3" t="s">
         <v>11</v>
@@ -12301,77 +12351,77 @@
         <v>2</v>
       </c>
       <c r="B17" s="44"/>
-      <c r="C17" s="102">
+      <c r="C17" s="107">
         <f>SUM(D7:D15)</f>
         <v>0</v>
       </c>
-      <c r="D17" s="102"/>
+      <c r="D17" s="107"/>
       <c r="E17" s="45"/>
-      <c r="F17" s="103">
+      <c r="F17" s="108">
         <f>SUM(G7:G15)</f>
         <v>0</v>
       </c>
-      <c r="G17" s="103"/>
+      <c r="G17" s="108"/>
       <c r="H17" s="45"/>
-      <c r="I17" s="102">
+      <c r="I17" s="107">
         <f>SUM(J7:J15)</f>
         <v>0</v>
       </c>
-      <c r="J17" s="102"/>
+      <c r="J17" s="107"/>
       <c r="K17" s="45"/>
-      <c r="L17" s="103">
+      <c r="L17" s="108">
         <f>SUM(M7:M15)</f>
         <v>0</v>
       </c>
-      <c r="M17" s="103"/>
+      <c r="M17" s="108"/>
       <c r="N17" s="45"/>
-      <c r="O17" s="102">
+      <c r="O17" s="107">
         <f>SUM(P7:P15)</f>
         <v>0</v>
       </c>
-      <c r="P17" s="102"/>
+      <c r="P17" s="107"/>
       <c r="Q17" s="45"/>
-      <c r="R17" s="103">
+      <c r="R17" s="108">
         <f>SUM(S7:S15)</f>
         <v>0</v>
       </c>
-      <c r="S17" s="103"/>
+      <c r="S17" s="108"/>
       <c r="T17" s="45"/>
-      <c r="U17" s="102">
+      <c r="U17" s="107">
         <f>SUM(V7:V15)</f>
         <v>0</v>
       </c>
-      <c r="V17" s="102"/>
+      <c r="V17" s="107"/>
       <c r="W17" s="45"/>
-      <c r="X17" s="103">
+      <c r="X17" s="108">
         <f>SUM(Y7:Y15)</f>
         <v>0</v>
       </c>
-      <c r="Y17" s="103"/>
+      <c r="Y17" s="108"/>
       <c r="Z17" s="45"/>
-      <c r="AA17" s="102">
+      <c r="AA17" s="107">
         <f>SUM(AB7:AB15)</f>
         <v>0</v>
       </c>
-      <c r="AB17" s="102"/>
+      <c r="AB17" s="107"/>
       <c r="AC17" s="45"/>
-      <c r="AD17" s="103">
+      <c r="AD17" s="108">
         <f>SUM(AE7:AE15)</f>
         <v>0</v>
       </c>
-      <c r="AE17" s="103"/>
+      <c r="AE17" s="108"/>
       <c r="AF17" s="45"/>
-      <c r="AG17" s="102">
+      <c r="AG17" s="107">
         <f>SUM(AH7:AH15)</f>
         <v>0</v>
       </c>
-      <c r="AH17" s="102"/>
+      <c r="AH17" s="107"/>
       <c r="AI17" s="45"/>
-      <c r="AJ17" s="103">
+      <c r="AJ17" s="108">
         <f>SUM(AK7:AK15)</f>
         <v>0</v>
       </c>
-      <c r="AK17" s="103"/>
+      <c r="AK17" s="108"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="D13:D15">
@@ -12386,11 +12436,6 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="13">
-    <mergeCell ref="A6:A14"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="L17:M17"/>
     <mergeCell ref="O17:P17"/>
     <mergeCell ref="AG17:AH17"/>
     <mergeCell ref="AJ17:AK17"/>
@@ -12399,6 +12444,11 @@
     <mergeCell ref="X17:Y17"/>
     <mergeCell ref="AA17:AB17"/>
     <mergeCell ref="AD17:AE17"/>
+    <mergeCell ref="A6:A14"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="L17:M17"/>
   </mergeCells>
   <conditionalFormatting sqref="A4">
     <cfRule type="iconSet" priority="1">
@@ -12441,12 +12491,12 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="107" t="s">
+      <c r="B2" s="101" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="2:6" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="109" t="s">
+      <c r="B3" s="103" t="s">
         <v>60</v>
       </c>
       <c r="C3" s="40"/>
@@ -12458,7 +12508,7 @@
       </c>
     </row>
     <row r="4" spans="2:6" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="108" t="s">
+      <c r="B4" s="102" t="s">
         <v>2</v>
       </c>
       <c r="E4" s="5" t="str" cm="1">
@@ -12471,7 +12521,7 @@
       </c>
     </row>
     <row r="5" spans="2:6" ht="13.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="110">
+      <c r="B5" s="104">
         <f>SUM(F4:F12)</f>
         <v>0</v>
       </c>
@@ -12608,15 +12658,15 @@
         <v>19</v>
       </c>
       <c r="J2" s="8"/>
-      <c r="K2" s="105" t="s">
+      <c r="K2" s="109" t="s">
         <v>31</v>
       </c>
-      <c r="L2" s="106"/>
+      <c r="L2" s="110"/>
       <c r="M2" s="92"/>
-      <c r="N2" s="105" t="s">
+      <c r="N2" s="109" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="106"/>
+      <c r="O2" s="110"/>
       <c r="P2" s="93"/>
     </row>
     <row r="3" spans="1:16" ht="15" x14ac:dyDescent="0.3">
@@ -12747,7 +12797,7 @@
       </c>
       <c r="L5" s="24">
         <f>SUM('Receitas - Mapa'!B4:M6)-SUM('Receitas - Mapa'!B15:M17)-SUM('Receitas - Mapa'!B9:M12)</f>
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="M5" s="15"/>
       <c r="N5" s="97" t="str">
@@ -12935,7 +12985,7 @@
       </c>
       <c r="L9" s="26">
         <f>'Despesas - Mapa'!AK4</f>
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="M9" s="16"/>
       <c r="N9" s="97" t="str">
@@ -12982,7 +13032,7 @@
       </c>
       <c r="L10" s="28">
         <f>'Gráfico - Anual'!D15</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M10" s="16"/>
       <c r="N10" s="97" t="str">
@@ -13044,11 +13094,11 @@
       <c r="B12" s="13"/>
       <c r="C12" s="23">
         <f>'Receitas - Mapa'!K19</f>
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D12" s="24">
         <f>SUM('Receitas - Mapa'!K16:K17)</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E12" s="15"/>
       <c r="F12" s="29">
@@ -13058,11 +13108,11 @@
       <c r="G12" s="16"/>
       <c r="H12" s="23">
         <f t="shared" si="0"/>
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="I12" s="26">
         <f>'Despesas - Mapa'!AE4</f>
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="J12" s="8"/>
       <c r="K12" s="93"/>
@@ -13098,7 +13148,7 @@
       </c>
       <c r="I13" s="26">
         <f>'Despesas - Mapa'!AH4</f>
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="J13" s="8"/>
       <c r="K13" s="93"/>
@@ -13134,7 +13184,7 @@
       </c>
       <c r="I14" s="26">
         <f>'Despesas - Mapa'!AK4</f>
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="J14" s="8"/>
       <c r="K14" s="93"/>
@@ -13151,11 +13201,11 @@
       <c r="B15" s="13"/>
       <c r="C15" s="25">
         <f>SUM(C3:C14)</f>
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D15" s="24">
         <f>SUM(D3:D14)</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E15" s="15"/>
       <c r="F15" s="29">
@@ -13168,7 +13218,7 @@
       </c>
       <c r="I15" s="28">
         <f>'Gráfico - Anual'!L9</f>
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="J15" s="8"/>
       <c r="K15" s="93"/>
@@ -13185,11 +13235,11 @@
       <c r="B16" s="13"/>
       <c r="C16" s="25">
         <f>AVERAGE(C3:C14)</f>
-        <v>12.5</v>
+        <v>8.3333333333333339</v>
       </c>
       <c r="D16" s="24">
         <f>AVERAGE(D3:D14)</f>
-        <v>0</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="E16" s="15"/>
       <c r="F16" s="30">
@@ -13243,11 +13293,11 @@
       <c r="B18" s="13"/>
       <c r="C18" s="27">
         <f>SUM($C$9:$C$14)</f>
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D18" s="28">
         <f>SUM($D$9:$D$14)</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E18" s="16"/>
       <c r="F18" s="32">

--- a/C. Financeiro 3.2.xlsx
+++ b/C. Financeiro 3.2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rcssi\Code\Personal_Finance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93A38CFF-437C-4C33-AF63-68576D29E7E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{003425B8-D0CB-437E-B681-49DF0B11FA58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-114" yWindow="-114" windowWidth="19704" windowHeight="11178" tabRatio="792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -592,7 +592,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -842,11 +842,11 @@
     <xf numFmtId="44" fontId="10" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="165" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -854,30 +854,18 @@
     <xf numFmtId="44" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Moeda" xfId="1" builtinId="4"/>
+    <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="13">
@@ -1156,7 +1144,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="pt-BR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2562,7 +2550,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="pt-BR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3314,7 +3302,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="pt-BR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3631,7 +3619,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="pt-BR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6595,7 +6583,7 @@
     <tableColumn id="6" xr3:uid="{23818CCC-08C7-4066-9B86-98D831460C75}" name="Operação" dataDxfId="6"/>
     <tableColumn id="3" xr3:uid="{78815540-1C3C-4370-A3E4-1C8E033CFC39}" name="Categoria" dataDxfId="5"/>
     <tableColumn id="7" xr3:uid="{F153B94E-6C60-4C63-A86C-8519A94E1F13}" name="Alocação" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{EE54C9A2-2D53-4D6A-93DF-88B691A8C3D9}" name="Valor" dataDxfId="3" dataCellStyle="Moeda"/>
+    <tableColumn id="4" xr3:uid="{EE54C9A2-2D53-4D6A-93DF-88B691A8C3D9}" name="Valor" dataDxfId="3"/>
     <tableColumn id="5" xr3:uid="{28149A80-D409-4A63-B4C2-6EDA92C21F54}" name="Descrição" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -6908,15 +6896,15 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="105" t="s">
+      <c r="B2" s="106" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105" t="str">
+      <c r="C2" s="106"/>
+      <c r="D2" s="106" t="str">
         <f ca="1">PROPER(TEXT(TODAY(),"MMMM"))</f>
         <v>Outubro</v>
       </c>
-      <c r="E2" s="105"/>
+      <c r="E2" s="106"/>
       <c r="F2" s="83"/>
       <c r="H2" s="82"/>
     </row>
@@ -7092,22 +7080,22 @@
       <c r="F12" s="79" t="s">
         <v>38</v>
       </c>
-      <c r="G12" s="111">
+      <c r="G12" s="105">
         <v>50</v>
       </c>
       <c r="H12" s="81"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B13" s="112"/>
-      <c r="C13" s="113" t="str">
+      <c r="B13" s="77"/>
+      <c r="C13" s="78" t="str">
         <f>IF(ISBLANK(B13),"",PROPER(TEXT(B13,"MMMM")))</f>
         <v/>
       </c>
       <c r="D13" s="78"/>
-      <c r="E13" s="114"/>
+      <c r="E13" s="79"/>
       <c r="F13" s="79"/>
-      <c r="G13" s="111"/>
-      <c r="H13" s="115"/>
+      <c r="G13" s="105"/>
+      <c r="H13" s="81"/>
     </row>
     <row r="22" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C22" s="84" t="str">
@@ -11323,7 +11311,7 @@
       <c r="AK5" s="39"/>
     </row>
     <row r="6" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="106" t="s">
+      <c r="A6" s="109" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="42"/>
@@ -11412,7 +11400,7 @@
       </c>
     </row>
     <row r="7" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="106"/>
+      <c r="A7" s="109"/>
       <c r="B7" s="42"/>
       <c r="C7" s="2" t="s">
         <v>27</v>
@@ -11522,7 +11510,7 @@
       </c>
     </row>
     <row r="8" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="106"/>
+      <c r="A8" s="109"/>
       <c r="B8" s="42"/>
       <c r="C8" s="2" t="s">
         <v>25</v>
@@ -11621,7 +11609,7 @@
       </c>
     </row>
     <row r="9" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="106"/>
+      <c r="A9" s="109"/>
       <c r="B9" s="42"/>
       <c r="C9" s="3" t="s">
         <v>26</v>
@@ -11720,7 +11708,7 @@
       </c>
     </row>
     <row r="10" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="106"/>
+      <c r="A10" s="109"/>
       <c r="B10" s="42"/>
       <c r="C10" s="3" t="s">
         <v>24</v>
@@ -11819,7 +11807,7 @@
       </c>
     </row>
     <row r="11" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="106"/>
+      <c r="A11" s="109"/>
       <c r="B11" s="42"/>
       <c r="C11" s="3" t="s">
         <v>23</v>
@@ -11918,7 +11906,7 @@
       </c>
     </row>
     <row r="12" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="106"/>
+      <c r="A12" s="109"/>
       <c r="B12" s="42"/>
       <c r="C12" s="3" t="s">
         <v>28</v>
@@ -12017,7 +12005,7 @@
       </c>
     </row>
     <row r="13" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="106"/>
+      <c r="A13" s="109"/>
       <c r="B13" s="42"/>
       <c r="C13" s="3" t="s">
         <v>13</v>
@@ -12116,7 +12104,7 @@
       </c>
     </row>
     <row r="14" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="106"/>
+      <c r="A14" s="109"/>
       <c r="B14" s="42"/>
       <c r="C14" s="3" t="s">
         <v>11</v>
@@ -12436,6 +12424,11 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="13">
+    <mergeCell ref="A6:A14"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="L17:M17"/>
     <mergeCell ref="O17:P17"/>
     <mergeCell ref="AG17:AH17"/>
     <mergeCell ref="AJ17:AK17"/>
@@ -12444,11 +12437,6 @@
     <mergeCell ref="X17:Y17"/>
     <mergeCell ref="AA17:AB17"/>
     <mergeCell ref="AD17:AE17"/>
-    <mergeCell ref="A6:A14"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="L17:M17"/>
   </mergeCells>
   <conditionalFormatting sqref="A4">
     <cfRule type="iconSet" priority="1">
@@ -12658,15 +12646,15 @@
         <v>19</v>
       </c>
       <c r="J2" s="8"/>
-      <c r="K2" s="109" t="s">
+      <c r="K2" s="110" t="s">
         <v>31</v>
       </c>
-      <c r="L2" s="110"/>
+      <c r="L2" s="111"/>
       <c r="M2" s="92"/>
-      <c r="N2" s="109" t="s">
+      <c r="N2" s="110" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="110"/>
+      <c r="O2" s="111"/>
       <c r="P2" s="93"/>
     </row>
     <row r="3" spans="1:16" ht="15" x14ac:dyDescent="0.3">

--- a/C. Financeiro 3.2.xlsx
+++ b/C. Financeiro 3.2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rcssi\Code\Personal_Finance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{003425B8-D0CB-437E-B681-49DF0B11FA58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D94C0FD-E68C-4A6B-8BAD-834B3977831B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-114" yWindow="-114" windowWidth="19704" windowHeight="11178" tabRatio="792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -848,14 +848,14 @@
     <xf numFmtId="165" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="44" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -865,7 +865,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Currency" xfId="1" builtinId="4"/>
+    <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="13">
@@ -1144,7 +1144,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="pt-BR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2550,7 +2550,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="pt-BR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3302,7 +3302,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="pt-BR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3619,7 +3619,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="pt-BR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6880,7 +6880,7 @@
   <sheetPr codeName="Planilha1">
     <tabColor theme="0"/>
   </sheetPr>
-  <dimension ref="A2:I549"/>
+  <dimension ref="A1:I549"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" style="82" customWidth="1"/>
@@ -6895,6 +6895,7 @@
     <col min="11" max="16384" width="9.140625" style="82"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="106" t="s">
         <v>4</v>
@@ -11311,7 +11312,7 @@
       <c r="AK5" s="39"/>
     </row>
     <row r="6" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="109" t="s">
+      <c r="A6" s="107" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="42"/>
@@ -11400,7 +11401,7 @@
       </c>
     </row>
     <row r="7" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="109"/>
+      <c r="A7" s="107"/>
       <c r="B7" s="42"/>
       <c r="C7" s="2" t="s">
         <v>27</v>
@@ -11510,7 +11511,7 @@
       </c>
     </row>
     <row r="8" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="109"/>
+      <c r="A8" s="107"/>
       <c r="B8" s="42"/>
       <c r="C8" s="2" t="s">
         <v>25</v>
@@ -11609,7 +11610,7 @@
       </c>
     </row>
     <row r="9" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="109"/>
+      <c r="A9" s="107"/>
       <c r="B9" s="42"/>
       <c r="C9" s="3" t="s">
         <v>26</v>
@@ -11708,7 +11709,7 @@
       </c>
     </row>
     <row r="10" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="109"/>
+      <c r="A10" s="107"/>
       <c r="B10" s="42"/>
       <c r="C10" s="3" t="s">
         <v>24</v>
@@ -11807,7 +11808,7 @@
       </c>
     </row>
     <row r="11" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="109"/>
+      <c r="A11" s="107"/>
       <c r="B11" s="42"/>
       <c r="C11" s="3" t="s">
         <v>23</v>
@@ -11906,7 +11907,7 @@
       </c>
     </row>
     <row r="12" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="109"/>
+      <c r="A12" s="107"/>
       <c r="B12" s="42"/>
       <c r="C12" s="3" t="s">
         <v>28</v>
@@ -12005,7 +12006,7 @@
       </c>
     </row>
     <row r="13" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="109"/>
+      <c r="A13" s="107"/>
       <c r="B13" s="42"/>
       <c r="C13" s="3" t="s">
         <v>13</v>
@@ -12104,7 +12105,7 @@
       </c>
     </row>
     <row r="14" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="109"/>
+      <c r="A14" s="107"/>
       <c r="B14" s="42"/>
       <c r="C14" s="3" t="s">
         <v>11</v>
@@ -12339,77 +12340,77 @@
         <v>2</v>
       </c>
       <c r="B17" s="44"/>
-      <c r="C17" s="107">
+      <c r="C17" s="108">
         <f>SUM(D7:D15)</f>
         <v>0</v>
       </c>
-      <c r="D17" s="107"/>
+      <c r="D17" s="108"/>
       <c r="E17" s="45"/>
-      <c r="F17" s="108">
+      <c r="F17" s="109">
         <f>SUM(G7:G15)</f>
         <v>0</v>
       </c>
-      <c r="G17" s="108"/>
+      <c r="G17" s="109"/>
       <c r="H17" s="45"/>
-      <c r="I17" s="107">
+      <c r="I17" s="108">
         <f>SUM(J7:J15)</f>
         <v>0</v>
       </c>
-      <c r="J17" s="107"/>
+      <c r="J17" s="108"/>
       <c r="K17" s="45"/>
-      <c r="L17" s="108">
+      <c r="L17" s="109">
         <f>SUM(M7:M15)</f>
         <v>0</v>
       </c>
-      <c r="M17" s="108"/>
+      <c r="M17" s="109"/>
       <c r="N17" s="45"/>
-      <c r="O17" s="107">
+      <c r="O17" s="108">
         <f>SUM(P7:P15)</f>
         <v>0</v>
       </c>
-      <c r="P17" s="107"/>
+      <c r="P17" s="108"/>
       <c r="Q17" s="45"/>
-      <c r="R17" s="108">
+      <c r="R17" s="109">
         <f>SUM(S7:S15)</f>
         <v>0</v>
       </c>
-      <c r="S17" s="108"/>
+      <c r="S17" s="109"/>
       <c r="T17" s="45"/>
-      <c r="U17" s="107">
+      <c r="U17" s="108">
         <f>SUM(V7:V15)</f>
         <v>0</v>
       </c>
-      <c r="V17" s="107"/>
+      <c r="V17" s="108"/>
       <c r="W17" s="45"/>
-      <c r="X17" s="108">
+      <c r="X17" s="109">
         <f>SUM(Y7:Y15)</f>
         <v>0</v>
       </c>
-      <c r="Y17" s="108"/>
+      <c r="Y17" s="109"/>
       <c r="Z17" s="45"/>
-      <c r="AA17" s="107">
+      <c r="AA17" s="108">
         <f>SUM(AB7:AB15)</f>
         <v>0</v>
       </c>
-      <c r="AB17" s="107"/>
+      <c r="AB17" s="108"/>
       <c r="AC17" s="45"/>
-      <c r="AD17" s="108">
+      <c r="AD17" s="109">
         <f>SUM(AE7:AE15)</f>
         <v>0</v>
       </c>
-      <c r="AE17" s="108"/>
+      <c r="AE17" s="109"/>
       <c r="AF17" s="45"/>
-      <c r="AG17" s="107">
+      <c r="AG17" s="108">
         <f>SUM(AH7:AH15)</f>
         <v>0</v>
       </c>
-      <c r="AH17" s="107"/>
+      <c r="AH17" s="108"/>
       <c r="AI17" s="45"/>
-      <c r="AJ17" s="108">
+      <c r="AJ17" s="109">
         <f>SUM(AK7:AK15)</f>
         <v>0</v>
       </c>
-      <c r="AK17" s="108"/>
+      <c r="AK17" s="109"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="D13:D15">
@@ -12424,11 +12425,6 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="13">
-    <mergeCell ref="A6:A14"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="L17:M17"/>
     <mergeCell ref="O17:P17"/>
     <mergeCell ref="AG17:AH17"/>
     <mergeCell ref="AJ17:AK17"/>
@@ -12437,6 +12433,11 @@
     <mergeCell ref="X17:Y17"/>
     <mergeCell ref="AA17:AB17"/>
     <mergeCell ref="AD17:AE17"/>
+    <mergeCell ref="A6:A14"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="L17:M17"/>
   </mergeCells>
   <conditionalFormatting sqref="A4">
     <cfRule type="iconSet" priority="1">

--- a/C. Financeiro 3.2.xlsx
+++ b/C. Financeiro 3.2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rcssi\Code\Personal_Finance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D94C0FD-E68C-4A6B-8BAD-834B3977831B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECB3C64D-A986-478B-A1C8-9AD161C825E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-114" yWindow="-114" windowWidth="19704" windowHeight="11178" tabRatio="792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="63">
   <si>
     <t>Mês</t>
   </si>
@@ -213,9 +213,6 @@
     <t>Anual</t>
   </si>
   <si>
-    <t>Planilha</t>
-  </si>
-  <si>
     <t>Receitas</t>
   </si>
   <si>
@@ -255,13 +252,16 @@
     <t xml:space="preserve">Descrição </t>
   </si>
   <si>
-    <t>Janeiro</t>
-  </si>
-  <si>
     <t>Perdas Outros</t>
   </si>
   <si>
     <t>Transferir</t>
+  </si>
+  <si>
+    <t>Acumulativo</t>
+  </si>
+  <si>
+    <t>Outubro</t>
   </si>
 </sst>
 </file>
@@ -405,7 +405,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -587,12 +587,38 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -839,17 +865,11 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="10" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="44" fontId="11" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -857,10 +877,22 @@
     <xf numFmtId="44" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1163,9 +1195,9 @@
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
           <c:x val="0"/>
-          <c:y val="2.5291336811539009E-3"/>
+          <c:y val="6.4124993504356423E-2"/>
           <c:w val="1"/>
-          <c:h val="0.79665076208681651"/>
+          <c:h val="0.73505465001472348"/>
         </c:manualLayout>
       </c:layout>
       <c:barChart>
@@ -6897,15 +6929,15 @@
   <sheetData>
     <row r="1" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="106" t="s">
+      <c r="B2" s="105" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="106"/>
-      <c r="D2" s="106" t="str">
+      <c r="C2" s="105"/>
+      <c r="D2" s="112" t="str">
         <f ca="1">PROPER(TEXT(TODAY(),"MMMM"))</f>
         <v>Outubro</v>
       </c>
-      <c r="E2" s="106"/>
+      <c r="E2" s="113"/>
       <c r="F2" s="83"/>
       <c r="H2" s="82"/>
     </row>
@@ -6918,7 +6950,7 @@
         <v>100</v>
       </c>
       <c r="D3" s="71" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E3" s="56">
         <f ca="1">VLOOKUP(D2,'Gráfico - Anual'!A3:I14,8,FALSE)</f>
@@ -6953,7 +6985,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="66" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="E5" s="56">
         <f ca="1">VLOOKUP(D2,'Gráfico - Anual'!A3:I14,9,FALSE)</f>
@@ -6964,7 +6996,7 @@
     </row>
     <row r="6" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="57" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C6" s="7">
         <f ca="1">SUM(C3:C5)</f>
@@ -7005,13 +7037,13 @@
         <v>0</v>
       </c>
       <c r="D9" s="73" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E9" s="74" t="s">
         <v>40</v>
       </c>
       <c r="F9" s="74" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G9" s="75" t="s">
         <v>32</v>
@@ -7029,7 +7061,7 @@
         <v>Outubro</v>
       </c>
       <c r="D10" s="78" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E10" s="79" t="s">
         <v>33</v>
@@ -7051,7 +7083,7 @@
         <v>Outubro</v>
       </c>
       <c r="D11" s="78" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E11" s="79" t="s">
         <v>37</v>
@@ -7076,12 +7108,12 @@
         <v>3</v>
       </c>
       <c r="E12" s="79" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F12" s="79" t="s">
         <v>38</v>
       </c>
-      <c r="G12" s="105">
+      <c r="G12" s="104">
         <v>50</v>
       </c>
       <c r="H12" s="81"/>
@@ -7095,7 +7127,7 @@
       <c r="D13" s="78"/>
       <c r="E13" s="79"/>
       <c r="F13" s="79"/>
-      <c r="G13" s="105"/>
+      <c r="G13" s="104"/>
       <c r="H13" s="81"/>
     </row>
     <row r="22" spans="3:9" x14ac:dyDescent="0.3">
@@ -10351,7 +10383,7 @@
     </row>
     <row r="3" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="65" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -10409,7 +10441,7 @@
     </row>
     <row r="5" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B5" s="7">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A5)</f>
@@ -10530,7 +10562,7 @@
     </row>
     <row r="8" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="65" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -10547,7 +10579,7 @@
     </row>
     <row r="9" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B9" s="7">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A9)</f>
@@ -10600,7 +10632,7 @@
     </row>
     <row r="10" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B10" s="7">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A10)</f>
@@ -10653,7 +10685,7 @@
     </row>
     <row r="11" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B11" s="7">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A11)</f>
@@ -10759,7 +10791,7 @@
     </row>
     <row r="13" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B13" s="76">
         <f>IF((SUM(B4:B6)-SUM(B9:B11)) &gt; 10, ((SUM(B4:B6)-SUM(B9:B11))*0.1), (0))-B12</f>
@@ -10844,7 +10876,7 @@
     </row>
     <row r="16" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B16" s="7">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A16)</f>
@@ -10897,7 +10929,7 @@
     </row>
     <row r="17" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B17" s="7">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A17)</f>
@@ -11312,7 +11344,7 @@
       <c r="AK5" s="39"/>
     </row>
     <row r="6" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="107" t="s">
+      <c r="A6" s="108" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="42"/>
@@ -11401,7 +11433,7 @@
       </c>
     </row>
     <row r="7" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="107"/>
+      <c r="A7" s="108"/>
       <c r="B7" s="42"/>
       <c r="C7" s="2" t="s">
         <v>27</v>
@@ -11511,7 +11543,7 @@
       </c>
     </row>
     <row r="8" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="107"/>
+      <c r="A8" s="108"/>
       <c r="B8" s="42"/>
       <c r="C8" s="2" t="s">
         <v>25</v>
@@ -11610,7 +11642,7 @@
       </c>
     </row>
     <row r="9" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="107"/>
+      <c r="A9" s="108"/>
       <c r="B9" s="42"/>
       <c r="C9" s="3" t="s">
         <v>26</v>
@@ -11709,7 +11741,7 @@
       </c>
     </row>
     <row r="10" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="107"/>
+      <c r="A10" s="108"/>
       <c r="B10" s="42"/>
       <c r="C10" s="3" t="s">
         <v>24</v>
@@ -11808,7 +11840,7 @@
       </c>
     </row>
     <row r="11" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="107"/>
+      <c r="A11" s="108"/>
       <c r="B11" s="42"/>
       <c r="C11" s="3" t="s">
         <v>23</v>
@@ -11907,7 +11939,7 @@
       </c>
     </row>
     <row r="12" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="107"/>
+      <c r="A12" s="108"/>
       <c r="B12" s="42"/>
       <c r="C12" s="3" t="s">
         <v>28</v>
@@ -12006,7 +12038,7 @@
       </c>
     </row>
     <row r="13" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="107"/>
+      <c r="A13" s="108"/>
       <c r="B13" s="42"/>
       <c r="C13" s="3" t="s">
         <v>13</v>
@@ -12105,7 +12137,7 @@
       </c>
     </row>
     <row r="14" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="107"/>
+      <c r="A14" s="108"/>
       <c r="B14" s="42"/>
       <c r="C14" s="3" t="s">
         <v>11</v>
@@ -12340,77 +12372,77 @@
         <v>2</v>
       </c>
       <c r="B17" s="44"/>
-      <c r="C17" s="108">
+      <c r="C17" s="106">
         <f>SUM(D7:D15)</f>
         <v>0</v>
       </c>
-      <c r="D17" s="108"/>
+      <c r="D17" s="106"/>
       <c r="E17" s="45"/>
-      <c r="F17" s="109">
+      <c r="F17" s="107">
         <f>SUM(G7:G15)</f>
         <v>0</v>
       </c>
-      <c r="G17" s="109"/>
+      <c r="G17" s="107"/>
       <c r="H17" s="45"/>
-      <c r="I17" s="108">
+      <c r="I17" s="106">
         <f>SUM(J7:J15)</f>
         <v>0</v>
       </c>
-      <c r="J17" s="108"/>
+      <c r="J17" s="106"/>
       <c r="K17" s="45"/>
-      <c r="L17" s="109">
+      <c r="L17" s="107">
         <f>SUM(M7:M15)</f>
         <v>0</v>
       </c>
-      <c r="M17" s="109"/>
+      <c r="M17" s="107"/>
       <c r="N17" s="45"/>
-      <c r="O17" s="108">
+      <c r="O17" s="106">
         <f>SUM(P7:P15)</f>
         <v>0</v>
       </c>
-      <c r="P17" s="108"/>
+      <c r="P17" s="106"/>
       <c r="Q17" s="45"/>
-      <c r="R17" s="109">
+      <c r="R17" s="107">
         <f>SUM(S7:S15)</f>
         <v>0</v>
       </c>
-      <c r="S17" s="109"/>
+      <c r="S17" s="107"/>
       <c r="T17" s="45"/>
-      <c r="U17" s="108">
+      <c r="U17" s="106">
         <f>SUM(V7:V15)</f>
         <v>0</v>
       </c>
-      <c r="V17" s="108"/>
+      <c r="V17" s="106"/>
       <c r="W17" s="45"/>
-      <c r="X17" s="109">
+      <c r="X17" s="107">
         <f>SUM(Y7:Y15)</f>
         <v>0</v>
       </c>
-      <c r="Y17" s="109"/>
+      <c r="Y17" s="107"/>
       <c r="Z17" s="45"/>
-      <c r="AA17" s="108">
+      <c r="AA17" s="106">
         <f>SUM(AB7:AB15)</f>
         <v>0</v>
       </c>
-      <c r="AB17" s="108"/>
+      <c r="AB17" s="106"/>
       <c r="AC17" s="45"/>
-      <c r="AD17" s="109">
+      <c r="AD17" s="107">
         <f>SUM(AE7:AE15)</f>
         <v>0</v>
       </c>
-      <c r="AE17" s="109"/>
+      <c r="AE17" s="107"/>
       <c r="AF17" s="45"/>
-      <c r="AG17" s="108">
+      <c r="AG17" s="106">
         <f>SUM(AH7:AH15)</f>
         <v>0</v>
       </c>
-      <c r="AH17" s="108"/>
+      <c r="AH17" s="106"/>
       <c r="AI17" s="45"/>
-      <c r="AJ17" s="109">
+      <c r="AJ17" s="107">
         <f>SUM(AK7:AK15)</f>
         <v>0</v>
       </c>
-      <c r="AK17" s="109"/>
+      <c r="AK17" s="107"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="D13:D15">
@@ -12425,6 +12457,11 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="13">
+    <mergeCell ref="A6:A14"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="L17:M17"/>
     <mergeCell ref="O17:P17"/>
     <mergeCell ref="AG17:AH17"/>
     <mergeCell ref="AJ17:AK17"/>
@@ -12433,11 +12470,6 @@
     <mergeCell ref="X17:Y17"/>
     <mergeCell ref="AA17:AB17"/>
     <mergeCell ref="AD17:AE17"/>
-    <mergeCell ref="A6:A14"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="L17:M17"/>
   </mergeCells>
   <conditionalFormatting sqref="A4">
     <cfRule type="iconSet" priority="1">
@@ -12486,11 +12518,11 @@
     </row>
     <row r="3" spans="2:6" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="103" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C3" s="40"/>
       <c r="E3" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F3" s="100" t="s">
         <v>32</v>
@@ -12509,8 +12541,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="13.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="104">
+    <row r="5" spans="2:6" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="111">
         <f>SUM(F4:F12)</f>
         <v>0</v>
       </c>
@@ -12521,7 +12553,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:6" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="102" t="s">
+        <v>4</v>
+      </c>
       <c r="E6" s="5" t="str">
         <v>Eletron e Jogos</v>
       </c>
@@ -12529,7 +12564,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:6" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="111">
+        <f>VLOOKUP(B3,'Gráfico - Anual'!A3:I14,9,FALSE)</f>
+        <v>100</v>
+      </c>
       <c r="E7" s="5" t="str">
         <v>Cursos</v>
       </c>
@@ -12647,15 +12686,15 @@
         <v>19</v>
       </c>
       <c r="J2" s="8"/>
-      <c r="K2" s="110" t="s">
+      <c r="K2" s="109" t="s">
         <v>31</v>
       </c>
-      <c r="L2" s="111"/>
+      <c r="L2" s="110"/>
       <c r="M2" s="92"/>
-      <c r="N2" s="110" t="s">
+      <c r="N2" s="109" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="111"/>
+      <c r="O2" s="110"/>
       <c r="P2" s="93"/>
     </row>
     <row r="3" spans="1:16" ht="15" x14ac:dyDescent="0.3">

--- a/C. Financeiro 3.2.xlsx
+++ b/C. Financeiro 3.2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rcssi\Code\Personal_Finance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECB3C64D-A986-478B-A1C8-9AD161C825E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFAEE27F-9EB1-44E5-840E-227871DE778E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-114" yWindow="-114" windowWidth="19704" windowHeight="11178" tabRatio="792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -130,9 +130,6 @@
   </si>
   <si>
     <t>Receita Líquida</t>
-  </si>
-  <si>
-    <t>Sld Acumu.</t>
   </si>
   <si>
     <t>Sld mês</t>
@@ -258,10 +255,13 @@
     <t>Transferir</t>
   </si>
   <si>
-    <t>Acumulativo</t>
+    <t>Outubro</t>
   </si>
   <si>
-    <t>Outubro</t>
+    <t>Atual</t>
+  </si>
+  <si>
+    <t>Sld. Atual</t>
   </si>
 </sst>
 </file>
@@ -868,8 +868,20 @@
     <xf numFmtId="44" fontId="11" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="44" fontId="10" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="165" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -877,22 +889,10 @@
     <xf numFmtId="44" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="10" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -6929,28 +6929,28 @@
   <sheetData>
     <row r="1" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="105" t="s">
+      <c r="B2" s="106" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="112" t="str">
+      <c r="C2" s="106"/>
+      <c r="D2" s="107" t="str">
         <f ca="1">PROPER(TEXT(TODAY(),"MMMM"))</f>
         <v>Outubro</v>
       </c>
-      <c r="E2" s="113"/>
+      <c r="E2" s="108"/>
       <c r="F2" s="83"/>
       <c r="H2" s="82"/>
     </row>
     <row r="3" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="57" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C3" s="7" cm="1">
         <f t="array" aca="1" ref="C3" ca="1">SUM(SUMIFS(Tabela1[Valor],Tabela1[Operação],{"Receitas";"Transferir"},Tabela1[Alocação],B3,Tabela1[Data],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Valor],Tabela1[Operação],"&lt;&gt;Receitas",Tabela1[Operação],"&lt;&gt;Transferir",Tabela1[Alocação],B3,Tabela1[Data],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Valor],Tabela1[Categoria],B3,Tabela1[Data],"&lt;="&amp;(TODAY()))</f>
         <v>100</v>
       </c>
       <c r="D3" s="71" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E3" s="56">
         <f ca="1">VLOOKUP(D2,'Gráfico - Anual'!A3:I14,8,FALSE)</f>
@@ -6960,14 +6960,14 @@
     </row>
     <row r="4" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="57" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C4" s="7" cm="1">
         <f t="array" aca="1" ref="C4" ca="1">SUM(SUMIFS(Tabela1[Valor],Tabela1[Operação],{"Receitas";"Transferir"},Tabela1[Alocação],B4,Tabela1[Data],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Valor],Tabela1[Operação],"&lt;&gt;Receitas",Tabela1[Operação],"&lt;&gt;Transferir",Tabela1[Alocação],B4,Tabela1[Data],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Valor],Tabela1[Categoria],B4,Tabela1[Data],"&lt;="&amp;(TODAY()))</f>
         <v>0</v>
       </c>
       <c r="D4" s="71" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E4" s="56">
         <f>'Gráfico - Anual'!I15</f>
@@ -6978,7 +6978,7 @@
     </row>
     <row r="5" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="57" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C5" s="7" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">SUM(SUMIFS(Tabela1[Valor],Tabela1[Operação],{"Receitas";"Transferir"},Tabela1[Alocação],B5,Tabela1[Data],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Valor],Tabela1[Operação],"&lt;&gt;Receitas",Tabela1[Operação],"&lt;&gt;Transferir",Tabela1[Alocação],B5,Tabela1[Data],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Valor],Tabela1[Categoria],B5,Tabela1[Data],"&lt;="&amp;(TODAY()))</f>
@@ -6996,14 +6996,14 @@
     </row>
     <row r="6" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="57" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C6" s="7">
         <f ca="1">SUM(C3:C5)</f>
         <v>100</v>
       </c>
       <c r="D6" s="66" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E6" s="56">
         <f ca="1">ROUND(C6-E5,2)</f>
@@ -7031,22 +7031,22 @@
     </row>
     <row r="9" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="72" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="73" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" s="74" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="73" t="s">
-        <v>54</v>
-      </c>
-      <c r="E9" s="74" t="s">
-        <v>40</v>
-      </c>
       <c r="F9" s="74" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G9" s="75" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H9" s="74" t="s">
         <v>15</v>
@@ -7061,13 +7061,13 @@
         <v>Outubro</v>
       </c>
       <c r="D10" s="78" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E10" s="79" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F10" s="79" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G10" s="80">
         <v>150</v>
@@ -7083,13 +7083,13 @@
         <v>Outubro</v>
       </c>
       <c r="D11" s="78" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E11" s="79" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" s="79" t="s">
         <v>37</v>
-      </c>
-      <c r="F11" s="79" t="s">
-        <v>38</v>
       </c>
       <c r="G11" s="80">
         <v>50</v>
@@ -7108,10 +7108,10 @@
         <v>3</v>
       </c>
       <c r="E12" s="79" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F12" s="79" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G12" s="104">
         <v>50</v>
@@ -7158,7 +7158,7 @@
         <v/>
       </c>
       <c r="I31" s="82" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="32" spans="3:9" x14ac:dyDescent="0.3">
@@ -10383,12 +10383,12 @@
     </row>
     <row r="3" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="65" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B4" s="7">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A4)</f>
@@ -10441,7 +10441,7 @@
     </row>
     <row r="5" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B5" s="7">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A5)</f>
@@ -10562,7 +10562,7 @@
     </row>
     <row r="8" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="65" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -10579,7 +10579,7 @@
     </row>
     <row r="9" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B9" s="7">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A9)</f>
@@ -10632,7 +10632,7 @@
     </row>
     <row r="10" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B10" s="7">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A10)</f>
@@ -10685,7 +10685,7 @@
     </row>
     <row r="11" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B11" s="7">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A11)</f>
@@ -10738,7 +10738,7 @@
     </row>
     <row r="12" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B12" s="7">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A12)</f>
@@ -10791,7 +10791,7 @@
     </row>
     <row r="13" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B13" s="76">
         <f>IF((SUM(B4:B6)-SUM(B9:B11)) &gt; 10, ((SUM(B4:B6)-SUM(B9:B11))*0.1), (0))-B12</f>
@@ -10876,7 +10876,7 @@
     </row>
     <row r="16" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B16" s="7">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A16)</f>
@@ -10929,7 +10929,7 @@
     </row>
     <row r="17" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B17" s="7">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A17)</f>
@@ -11344,7 +11344,7 @@
       <c r="AK5" s="39"/>
     </row>
     <row r="6" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="108" t="s">
+      <c r="A6" s="109" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="42"/>
@@ -11352,91 +11352,91 @@
         <v>15</v>
       </c>
       <c r="D6" s="47" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E6" s="39"/>
       <c r="F6" s="48" t="s">
         <v>15</v>
       </c>
       <c r="G6" s="49" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H6" s="39"/>
       <c r="I6" s="46" t="s">
         <v>15</v>
       </c>
       <c r="J6" s="47" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K6" s="39"/>
       <c r="L6" s="48" t="s">
         <v>15</v>
       </c>
       <c r="M6" s="49" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N6" s="39"/>
       <c r="O6" s="46" t="s">
         <v>15</v>
       </c>
       <c r="P6" s="47" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q6" s="39"/>
       <c r="R6" s="48" t="s">
         <v>15</v>
       </c>
       <c r="S6" s="49" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T6" s="39"/>
       <c r="U6" s="46" t="s">
         <v>15</v>
       </c>
       <c r="V6" s="47" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="W6" s="39"/>
       <c r="X6" s="48" t="s">
         <v>15</v>
       </c>
       <c r="Y6" s="49" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Z6" s="39"/>
       <c r="AA6" s="46" t="s">
         <v>15</v>
       </c>
       <c r="AB6" s="47" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AC6" s="39"/>
       <c r="AD6" s="48" t="s">
         <v>15</v>
       </c>
       <c r="AE6" s="49" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AF6" s="39"/>
       <c r="AG6" s="46" t="s">
         <v>15</v>
       </c>
       <c r="AH6" s="47" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AI6" s="39"/>
       <c r="AJ6" s="48" t="s">
         <v>15</v>
       </c>
       <c r="AK6" s="49" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="108"/>
+      <c r="A7" s="109"/>
       <c r="B7" s="42"/>
       <c r="C7" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D7" s="4">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!D$2,Tabela1[Categoria],'Despesas - Mapa'!C7)</f>
@@ -11543,10 +11543,10 @@
       </c>
     </row>
     <row r="8" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="108"/>
+      <c r="A8" s="109"/>
       <c r="B8" s="42"/>
       <c r="C8" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D8" s="4">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!D$2,Tabela1[Categoria],'Despesas - Mapa'!C8)</f>
@@ -11642,10 +11642,10 @@
       </c>
     </row>
     <row r="9" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="108"/>
+      <c r="A9" s="109"/>
       <c r="B9" s="42"/>
       <c r="C9" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D9" s="4">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!D$2,Tabela1[Categoria],'Despesas - Mapa'!C9)</f>
@@ -11741,10 +11741,10 @@
       </c>
     </row>
     <row r="10" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="108"/>
+      <c r="A10" s="109"/>
       <c r="B10" s="42"/>
       <c r="C10" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D10" s="4">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!D$2,Tabela1[Categoria],'Despesas - Mapa'!C10)</f>
@@ -11840,10 +11840,10 @@
       </c>
     </row>
     <row r="11" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="108"/>
+      <c r="A11" s="109"/>
       <c r="B11" s="42"/>
       <c r="C11" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D11" s="4">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!D$2,Tabela1[Categoria],'Despesas - Mapa'!C11)</f>
@@ -11939,10 +11939,10 @@
       </c>
     </row>
     <row r="12" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="108"/>
+      <c r="A12" s="109"/>
       <c r="B12" s="42"/>
       <c r="C12" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D12" s="4">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!D$2,Tabela1[Categoria],'Despesas - Mapa'!C12)</f>
@@ -12038,7 +12038,7 @@
       </c>
     </row>
     <row r="13" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="108"/>
+      <c r="A13" s="109"/>
       <c r="B13" s="42"/>
       <c r="C13" s="3" t="s">
         <v>13</v>
@@ -12137,7 +12137,7 @@
       </c>
     </row>
     <row r="14" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="108"/>
+      <c r="A14" s="109"/>
       <c r="B14" s="42"/>
       <c r="C14" s="3" t="s">
         <v>11</v>
@@ -12239,7 +12239,7 @@
       <c r="A15" s="67"/>
       <c r="B15" s="43"/>
       <c r="C15" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D15" s="4">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!D$2,Tabela1[Categoria],'Despesas - Mapa'!C15)</f>
@@ -12372,77 +12372,77 @@
         <v>2</v>
       </c>
       <c r="B17" s="44"/>
-      <c r="C17" s="106">
+      <c r="C17" s="110">
         <f>SUM(D7:D15)</f>
         <v>0</v>
       </c>
-      <c r="D17" s="106"/>
+      <c r="D17" s="110"/>
       <c r="E17" s="45"/>
-      <c r="F17" s="107">
+      <c r="F17" s="111">
         <f>SUM(G7:G15)</f>
         <v>0</v>
       </c>
-      <c r="G17" s="107"/>
+      <c r="G17" s="111"/>
       <c r="H17" s="45"/>
-      <c r="I17" s="106">
+      <c r="I17" s="110">
         <f>SUM(J7:J15)</f>
         <v>0</v>
       </c>
-      <c r="J17" s="106"/>
+      <c r="J17" s="110"/>
       <c r="K17" s="45"/>
-      <c r="L17" s="107">
+      <c r="L17" s="111">
         <f>SUM(M7:M15)</f>
         <v>0</v>
       </c>
-      <c r="M17" s="107"/>
+      <c r="M17" s="111"/>
       <c r="N17" s="45"/>
-      <c r="O17" s="106">
+      <c r="O17" s="110">
         <f>SUM(P7:P15)</f>
         <v>0</v>
       </c>
-      <c r="P17" s="106"/>
+      <c r="P17" s="110"/>
       <c r="Q17" s="45"/>
-      <c r="R17" s="107">
+      <c r="R17" s="111">
         <f>SUM(S7:S15)</f>
         <v>0</v>
       </c>
-      <c r="S17" s="107"/>
+      <c r="S17" s="111"/>
       <c r="T17" s="45"/>
-      <c r="U17" s="106">
+      <c r="U17" s="110">
         <f>SUM(V7:V15)</f>
         <v>0</v>
       </c>
-      <c r="V17" s="106"/>
+      <c r="V17" s="110"/>
       <c r="W17" s="45"/>
-      <c r="X17" s="107">
+      <c r="X17" s="111">
         <f>SUM(Y7:Y15)</f>
         <v>0</v>
       </c>
-      <c r="Y17" s="107"/>
+      <c r="Y17" s="111"/>
       <c r="Z17" s="45"/>
-      <c r="AA17" s="106">
+      <c r="AA17" s="110">
         <f>SUM(AB7:AB15)</f>
         <v>0</v>
       </c>
-      <c r="AB17" s="106"/>
+      <c r="AB17" s="110"/>
       <c r="AC17" s="45"/>
-      <c r="AD17" s="107">
+      <c r="AD17" s="111">
         <f>SUM(AE7:AE15)</f>
         <v>0</v>
       </c>
-      <c r="AE17" s="107"/>
+      <c r="AE17" s="111"/>
       <c r="AF17" s="45"/>
-      <c r="AG17" s="106">
+      <c r="AG17" s="110">
         <f>SUM(AH7:AH15)</f>
         <v>0</v>
       </c>
-      <c r="AH17" s="106"/>
+      <c r="AH17" s="110"/>
       <c r="AI17" s="45"/>
-      <c r="AJ17" s="107">
+      <c r="AJ17" s="111">
         <f>SUM(AK7:AK15)</f>
         <v>0</v>
       </c>
-      <c r="AK17" s="107"/>
+      <c r="AK17" s="111"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="D13:D15">
@@ -12457,11 +12457,6 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="13">
-    <mergeCell ref="A6:A14"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="L17:M17"/>
     <mergeCell ref="O17:P17"/>
     <mergeCell ref="AG17:AH17"/>
     <mergeCell ref="AJ17:AK17"/>
@@ -12470,6 +12465,11 @@
     <mergeCell ref="X17:Y17"/>
     <mergeCell ref="AA17:AB17"/>
     <mergeCell ref="AD17:AE17"/>
+    <mergeCell ref="A6:A14"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="L17:M17"/>
   </mergeCells>
   <conditionalFormatting sqref="A4">
     <cfRule type="iconSet" priority="1">
@@ -12518,14 +12518,14 @@
     </row>
     <row r="3" spans="2:6" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="103" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C3" s="40"/>
       <c r="E3" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F3" s="100" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="2:6" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
@@ -12542,7 +12542,7 @@
       </c>
     </row>
     <row r="5" spans="2:6" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="111">
+      <c r="B5" s="105">
         <f>SUM(F4:F12)</f>
         <v>0</v>
       </c>
@@ -12565,7 +12565,7 @@
       </c>
     </row>
     <row r="7" spans="2:6" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="111">
+      <c r="B7" s="105">
         <f>VLOOKUP(B3,'Gráfico - Anual'!A3:I14,9,FALSE)</f>
         <v>100</v>
       </c>
@@ -12669,7 +12669,7 @@
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D2" s="22" t="s">
         <v>3</v>
@@ -12680,21 +12680,21 @@
       </c>
       <c r="G2" s="13"/>
       <c r="H2" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I2" s="20" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="J2" s="8"/>
-      <c r="K2" s="109" t="s">
-        <v>31</v>
-      </c>
-      <c r="L2" s="110"/>
+      <c r="K2" s="112" t="s">
+        <v>30</v>
+      </c>
+      <c r="L2" s="113"/>
       <c r="M2" s="92"/>
-      <c r="N2" s="109" t="s">
+      <c r="N2" s="112" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="110"/>
+      <c r="O2" s="113"/>
       <c r="P2" s="93"/>
     </row>
     <row r="3" spans="1:16" ht="15" x14ac:dyDescent="0.3">
@@ -12868,7 +12868,7 @@
       </c>
       <c r="J6" s="8"/>
       <c r="K6" s="95" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L6" s="24">
         <f>SUM('Despesas - Mapa'!D7:D14,'Despesas - Mapa'!G7:G14,'Despesas - Mapa'!J7:J14,'Despesas - Mapa'!M7:M14,'Despesas - Mapa'!P7:P14,'Despesas - Mapa'!S7:S14,'Despesas - Mapa'!V7:V14,'Despesas - Mapa'!Y7:Y14,'Despesas - Mapa'!AB7:AB14,'Despesas - Mapa'!AE7:AE14,'Despesas - Mapa'!AH7:AH14,'Despesas - Mapa'!AK7:AK14)</f>
@@ -12915,7 +12915,7 @@
       </c>
       <c r="J7" s="8"/>
       <c r="K7" s="95" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L7" s="24">
         <f>SUM('Despesas - Mapa'!D15:D15,'Despesas - Mapa'!G15:G15,'Despesas - Mapa'!J15:J15,'Despesas - Mapa'!M15:M15,'Despesas - Mapa'!P15:P15,'Despesas - Mapa'!S15:S15,'Despesas - Mapa'!V15:V15,'Despesas - Mapa'!Y15:Y15,'Despesas - Mapa'!AB15:AB15,'Despesas - Mapa'!AE15:AE15,'Despesas - Mapa'!AH15:AH15,'Despesas - Mapa'!AK15:AK15)</f>
@@ -12962,7 +12962,7 @@
       </c>
       <c r="J8" s="8"/>
       <c r="K8" s="95" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L8" s="24">
         <f>SUM(L6:L7)</f>
@@ -13287,7 +13287,7 @@
     </row>
     <row r="17" spans="1:16" ht="15" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B17" s="13"/>
       <c r="C17" s="23">
@@ -13316,7 +13316,7 @@
     </row>
     <row r="18" spans="1:16" ht="15.7" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B18" s="13"/>
       <c r="C18" s="27">

--- a/C. Financeiro 3.2.xlsx
+++ b/C. Financeiro 3.2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rcssi\Code\Personal_Finance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFAEE27F-9EB1-44E5-840E-227871DE778E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77D7075E-265B-4309-AC63-980D3FBF1F4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-114" yWindow="-114" windowWidth="19704" windowHeight="11178" tabRatio="792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -880,14 +880,14 @@
     <xf numFmtId="165" fontId="9" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="44" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6935,7 +6935,7 @@
       <c r="C2" s="106"/>
       <c r="D2" s="107" t="str">
         <f ca="1">PROPER(TEXT(TODAY(),"MMMM"))</f>
-        <v>Outubro</v>
+        <v>Novembro</v>
       </c>
       <c r="E2" s="108"/>
       <c r="F2" s="83"/>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="E3" s="56">
         <f ca="1">VLOOKUP(D2,'Gráfico - Anual'!A3:I14,8,FALSE)</f>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H3" s="82"/>
     </row>
@@ -11344,7 +11344,7 @@
       <c r="AK5" s="39"/>
     </row>
     <row r="6" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="109" t="s">
+      <c r="A6" s="111" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="42"/>
@@ -11433,7 +11433,7 @@
       </c>
     </row>
     <row r="7" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="109"/>
+      <c r="A7" s="111"/>
       <c r="B7" s="42"/>
       <c r="C7" s="2" t="s">
         <v>26</v>
@@ -11543,7 +11543,7 @@
       </c>
     </row>
     <row r="8" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="109"/>
+      <c r="A8" s="111"/>
       <c r="B8" s="42"/>
       <c r="C8" s="2" t="s">
         <v>24</v>
@@ -11642,7 +11642,7 @@
       </c>
     </row>
     <row r="9" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="109"/>
+      <c r="A9" s="111"/>
       <c r="B9" s="42"/>
       <c r="C9" s="3" t="s">
         <v>25</v>
@@ -11741,7 +11741,7 @@
       </c>
     </row>
     <row r="10" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="109"/>
+      <c r="A10" s="111"/>
       <c r="B10" s="42"/>
       <c r="C10" s="3" t="s">
         <v>23</v>
@@ -11840,7 +11840,7 @@
       </c>
     </row>
     <row r="11" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="109"/>
+      <c r="A11" s="111"/>
       <c r="B11" s="42"/>
       <c r="C11" s="3" t="s">
         <v>22</v>
@@ -11939,7 +11939,7 @@
       </c>
     </row>
     <row r="12" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="109"/>
+      <c r="A12" s="111"/>
       <c r="B12" s="42"/>
       <c r="C12" s="3" t="s">
         <v>27</v>
@@ -12038,7 +12038,7 @@
       </c>
     </row>
     <row r="13" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="109"/>
+      <c r="A13" s="111"/>
       <c r="B13" s="42"/>
       <c r="C13" s="3" t="s">
         <v>13</v>
@@ -12137,7 +12137,7 @@
       </c>
     </row>
     <row r="14" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="109"/>
+      <c r="A14" s="111"/>
       <c r="B14" s="42"/>
       <c r="C14" s="3" t="s">
         <v>11</v>
@@ -12372,77 +12372,77 @@
         <v>2</v>
       </c>
       <c r="B17" s="44"/>
-      <c r="C17" s="110">
+      <c r="C17" s="109">
         <f>SUM(D7:D15)</f>
         <v>0</v>
       </c>
-      <c r="D17" s="110"/>
+      <c r="D17" s="109"/>
       <c r="E17" s="45"/>
-      <c r="F17" s="111">
+      <c r="F17" s="110">
         <f>SUM(G7:G15)</f>
         <v>0</v>
       </c>
-      <c r="G17" s="111"/>
+      <c r="G17" s="110"/>
       <c r="H17" s="45"/>
-      <c r="I17" s="110">
+      <c r="I17" s="109">
         <f>SUM(J7:J15)</f>
         <v>0</v>
       </c>
-      <c r="J17" s="110"/>
+      <c r="J17" s="109"/>
       <c r="K17" s="45"/>
-      <c r="L17" s="111">
+      <c r="L17" s="110">
         <f>SUM(M7:M15)</f>
         <v>0</v>
       </c>
-      <c r="M17" s="111"/>
+      <c r="M17" s="110"/>
       <c r="N17" s="45"/>
-      <c r="O17" s="110">
+      <c r="O17" s="109">
         <f>SUM(P7:P15)</f>
         <v>0</v>
       </c>
-      <c r="P17" s="110"/>
+      <c r="P17" s="109"/>
       <c r="Q17" s="45"/>
-      <c r="R17" s="111">
+      <c r="R17" s="110">
         <f>SUM(S7:S15)</f>
         <v>0</v>
       </c>
-      <c r="S17" s="111"/>
+      <c r="S17" s="110"/>
       <c r="T17" s="45"/>
-      <c r="U17" s="110">
+      <c r="U17" s="109">
         <f>SUM(V7:V15)</f>
         <v>0</v>
       </c>
-      <c r="V17" s="110"/>
+      <c r="V17" s="109"/>
       <c r="W17" s="45"/>
-      <c r="X17" s="111">
+      <c r="X17" s="110">
         <f>SUM(Y7:Y15)</f>
         <v>0</v>
       </c>
-      <c r="Y17" s="111"/>
+      <c r="Y17" s="110"/>
       <c r="Z17" s="45"/>
-      <c r="AA17" s="110">
+      <c r="AA17" s="109">
         <f>SUM(AB7:AB15)</f>
         <v>0</v>
       </c>
-      <c r="AB17" s="110"/>
+      <c r="AB17" s="109"/>
       <c r="AC17" s="45"/>
-      <c r="AD17" s="111">
+      <c r="AD17" s="110">
         <f>SUM(AE7:AE15)</f>
         <v>0</v>
       </c>
-      <c r="AE17" s="111"/>
+      <c r="AE17" s="110"/>
       <c r="AF17" s="45"/>
-      <c r="AG17" s="110">
+      <c r="AG17" s="109">
         <f>SUM(AH7:AH15)</f>
         <v>0</v>
       </c>
-      <c r="AH17" s="110"/>
+      <c r="AH17" s="109"/>
       <c r="AI17" s="45"/>
-      <c r="AJ17" s="111">
+      <c r="AJ17" s="110">
         <f>SUM(AK7:AK15)</f>
         <v>0</v>
       </c>
-      <c r="AK17" s="111"/>
+      <c r="AK17" s="110"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="D13:D15">
@@ -12457,6 +12457,11 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="13">
+    <mergeCell ref="A6:A14"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="L17:M17"/>
     <mergeCell ref="O17:P17"/>
     <mergeCell ref="AG17:AH17"/>
     <mergeCell ref="AJ17:AK17"/>
@@ -12465,11 +12470,6 @@
     <mergeCell ref="X17:Y17"/>
     <mergeCell ref="AA17:AB17"/>
     <mergeCell ref="AD17:AE17"/>
-    <mergeCell ref="A6:A14"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="L17:M17"/>
   </mergeCells>
   <conditionalFormatting sqref="A4">
     <cfRule type="iconSet" priority="1">
@@ -12943,7 +12943,7 @@
         <v>0</v>
       </c>
       <c r="D8" s="24">
-        <f>SUM('Receitas - Mapa'!G17:G51)</f>
+        <f>SUM('Receitas - Mapa'!G16:G17)</f>
         <v>0</v>
       </c>
       <c r="E8" s="15"/>
